--- a/output/cluster_vergleich/486073_CHT_Germany_GmbH_cluster.xlsx
+++ b/output/cluster_vergleich/486073_CHT_Germany_GmbH_cluster.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="CHT Germany GmbH" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NK_Konditionen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,4 +594,1041 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Schlüssel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Aktiv</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Aktive 
+Sendung 
+in Import- 
+/Export-
+Land</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Prüfung ERKA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>wird geprüft 
+von</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>betrifft
+Abrechnung</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>betrifft
+Erfassung
+(manuell)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>betrifft
+EDI</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>betrifft
+Operative/
+Abfertigung</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Filler2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>DFÜ 
+ja / Nein</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Bemerkungen AX-Team</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Umsatz 2024 P1-P9</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>PSS</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>PSS Umsatz 2024-2025</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Name, Straße, LKZ, PLZ Ort</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Check Sendung 2024-2025</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Column2
+SSS Satzart → Transportart:
+•1 – National
+•2 – Import
+•3 – Export
+•0 – Nicht 
+relevant</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Bemerkung / Hinweis für AX</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Benutzergruppe
+•0 - Alle Benutzer     
+•5 - Abrechnung debitorisch 
+•6 - Abrechnung kreditorisch
+•1 / 2 / 3 / 4 / 8 – Nicht relevant</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Prüfungshinweis
+grün -&gt; in AX hinterlegt
+pink-&gt; in AX zu hinterlegen
+rot -&gt; in AX nicht relevant
+orange -&gt; in AX Routing prüfen/umsetzen
+blau -&gt; EDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>174740</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>395080.19</v>
+      </c>
+      <c r="N2" t="n">
+        <v>17474</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>CHT R.BEITLICH GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>&gt;&gt; BITTE NEUE KUNDENNUMMER 27474 VERWENDEN |    ODER CHT10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>274742</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3 - wird benötigt in der Abrechnung</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>185</v>
+      </c>
+      <c r="N3" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O3" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>betrifft Konditionierung</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>IMPORTE ABRECHNEN - WERDEN NICHT BEGUTSCHRIFTET !</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>163173GR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3 - wird benötigt in der Abrechnung</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>697.6799999999999</v>
+      </c>
+      <c r="N4" t="n">
+        <v>16317</v>
+      </c>
+      <c r="O4" t="n">
+        <v>16317</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CHT SWITZERLAND AG,  KRIESSERNSTR. 20,  CH  9462  MONTLINGEN</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>163173GR</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Hinweis für Operative offen
+Abrechnungshinweis offen</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>GEHÖRT ZU CHT TÜBINGEN. | ABRECHNUNG ANALOG CHT - OFFERTE ABER NICHT GESPL. | ERFASST,DA BISHER NUR 1 SDG. PRO LKW. | THERMOVERLADUNG 150 € (MAN.ERF.) | EVTL. KLÄREN, OB DAS VIELLEICHT ADR-VERLADUNG | HEISSEN MÜSSTE (DENN CHT ZAHLT ADR ZUSCHLAG IN | DIESER HÖHE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>274742GB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>185</v>
+      </c>
+      <c r="N5" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O5" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>VERZOLLUNG EURO 75,00//EURO 5,00/ZOLLPOS AB 2.POS | ***MIT HR***</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>274742</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4 - betrifft Erfassung/ Abfertigung/ Operative</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>185</v>
+      </c>
+      <c r="N6" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O6" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>DIE ANLIEFERUNG FINDET GENERELL IN DUSSLINGEN | STATT -&gt; CHT10 !!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>274742E</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>185</v>
+      </c>
+      <c r="N7" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O7" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>&gt;&gt;&gt; IMPORT = EXPORT &lt;&lt;&lt; | KEIN ADR-ZUSCHLAG!</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>274742I</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>185</v>
+      </c>
+      <c r="N8" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O8" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>&gt;&gt; BITTE LIEFERSCHEINKOPIE IN AKTE LASSEN + |    BESTELLNUMMER ERFASSEN | &gt;&gt; VORSICHT !! KUNDE GIBT AB UND AN MAßE IN |    MILLIMETER AN !!</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>274742I</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>185</v>
+      </c>
+      <c r="N9" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O9" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>PRÜFEN, OB LSU FRACHTZAHLER IST, WENN KEINE | UNTERLAGEN IN AKTE SIND, VERGLEICHSSENDUNGEN | WENN LSU, DANN ABTEILUNG FRAGEN, WO LADEAUFTRAG | AUF EINZELRECHNUNG ÄNDERN!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>274743B</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>185</v>
+      </c>
+      <c r="N10" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O10" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>BEI FT FÜR DEN EMPFÄNGER DENY, B 8930 | MUSS BEI TERMIN FT EINGETRAGEN WERDEN DAMIT DIE | KOSTEN VON 75 EURO WEITERBERECHNET WERDEN !</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>274743CH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>185</v>
+      </c>
+      <c r="N11" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O11" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>AN EMPFÄNGER OSPELT 10073 KEINE VERZOLLUNG | ABRECHNEN!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>274743FL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>185</v>
+      </c>
+      <c r="N12" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O12" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>AN EMPFÄNGER OSPELT 10073 KEINE VERZOLLUNG | ABRECHNEN!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>274743GR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>185</v>
+      </c>
+      <c r="N13" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O13" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>BITTE CHT11 VERWENDEN !</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>274743I</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>185</v>
+      </c>
+      <c r="N14" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O14" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>&gt; BITTE VOLUMEN ERFASSEN !</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>274743I</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>185</v>
+      </c>
+      <c r="N15" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O15" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>5</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>&gt;&gt; VOLUMEN MUSS ERFASST SEIN !</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>274743L</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>185</v>
+      </c>
+      <c r="N16" t="n">
+        <v>27474</v>
+      </c>
+      <c r="O16" t="n">
+        <v>27474</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CHT GERMANY GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>3</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>&gt; SENDUNGEN WERDEN NICHT GUTGESCHRIEBEN. | &gt; FÜR LUXEMBURG = KEINE OFFERTE = ANFRAGEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>158590</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>15859</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CHT R.BEITLICH GMBH,  BISMARCKSTR. 102,  D  72072  TUEBINGEN</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>&gt;&gt; BITTE NEUE KUNDENNUMMER CHT11 VERWENDEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>